--- a/site/BSwift-to-ADP-API-Central-Integration-Guide/headings.xlsx
+++ b/site/BSwift-to-ADP-API-Central-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Benefits Sync Settings</t>
+          <t>Workers Sync Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,63 +671,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01KERQXQC13KRN7RYV8BYH5D3M</t>
+          <t>h_01KHAR2NNHP6QPQG78YWERFWE1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01KERQXQC13KRN7RYV8BYH5D3M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01KHAR2NNHP6QPQG78YWERFWE1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Worker Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01K5TXWEG9QVYTG8WCYTN8SJ58</t>
+          <t>h_01KHB9KHWVZA83VYFMZNHR3DMA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TXWEG9QVYTG8WCYTN8SJ58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01KHB9KHWVZA83VYFMZNHR3DMA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>CSV Column Header Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KHB9KHWVXYQDYFMSK2MY2X0G</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01KHB9KHWVXYQDYFMSK2MY2X0G</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Benefits Sync Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY3EN4QF917HX732APHYFT</t>
+          <t>01KERQXQC13KRN7RYV8BYH5D3M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY3EN4QF917HX732APHYFT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01KERQXQC13KRN7RYV8BYH5D3M</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,142 +759,230 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TXWEG9QVYTG8WCYTN8SJ58</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TXWEG9QVYTG8WCYTN8SJ58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Admin Notification Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY4V4B9MPS45NWNY829Z3F</t>
+          <t>01K5TY3EN4QF917HX732APHYFT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY4V4B9MPS45NWNY829Z3F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY3EN4QF917HX732APHYFT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Admin Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01K5TY4V4B9MPS45NWNY829Z3F</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#01K5TY4V4B9MPS45NWNY829Z3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KHB3FH2HS3R9APE8284T41M3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01KHB3FH2HS3R9APE8284T41M3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mapping Sections</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KHB3AWGXPZEQS9M5QDT0X0PB</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01KHB3AWGXPZEQS9M5QDT0X0PB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/BSwift-to-ADP-API-Central-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
